--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/110-creation-exemples/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
